--- a/reports/Make-List-NoStock-2026-10-26.xlsx
+++ b/reports/Make-List-NoStock-2026-10-26.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -94,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,6 +116,12 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2030,6 +2040,241 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>THE PLAN, PLANT BY PLANT — MT of tube</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Same 509.21 MT, nothing added. Columns are the tube thickness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>1.6 mm</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>2 mm</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>2.5 mm</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>2.8 mm</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>3 mm</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>4 mm</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>5 mm</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="H59" s="11" t="n"/>
+      <c r="I59" s="18" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>119.35</v>
+      </c>
+      <c r="K59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Lepakshi</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H60" s="11" t="n"/>
+      <c r="I60" s="18" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>59.79</v>
+      </c>
+      <c r="K60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>NPMD</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="11" t="n"/>
+      <c r="I61" s="18" t="n">
+        <v>256.1</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>202.1</v>
+      </c>
+      <c r="K61" s="11" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Tapi</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G62" s="11" t="n">
+        <v>59.07</v>
+      </c>
+      <c r="H62" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="I62" s="18" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="K62" s="11" t="n">
+        <v>29.07</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n">
+        <v>160.14</v>
+      </c>
+      <c r="C63" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D63" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E63" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F63" s="18" t="n">
+        <v>113</v>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="I63" s="18" t="n">
+        <v>509.21</v>
+      </c>
+      <c r="J63" s="18" t="n">
+        <v>426.14</v>
+      </c>
+      <c r="K63" s="18" t="n">
+        <v>83.06999999999999</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Blank cell = that plant makes nothing at that thickness this cycle. South is Hyderabad + Lepakshi, West is NPMD + Tapi; a plant only ever makes for its own region.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/Make-List-NoStock-2026-10-26.xlsx
+++ b/reports/Make-List-NoStock-2026-10-26.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Make List" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Make List'!$A$4:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Make List'!$A$5:$G$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -509,374 +509,348 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As on 26 Oct 2026. Only the sizes that clear both floors AND have the coil for them. One line per plant per coil. MT = tube to make. Everything deferred or blocked is left out — it is in Rolling-Plan-NoStock-2026-10-26.xlsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Coil position as at 27 Oct 2026 05:19 UTC. Only the sizes that clear both floors AND have the coil for them. MT = tube to make. Everything deferred or blocked is left out — it is in Rolling-Plan-NoStock-2026-10-26.xlsx. Anything slit or produced after the snapshot is not reflected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>"Coil to use" is a coil SPEC, not a single coil: a line may draw more than one physical coil of that thickness × width at that plant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Plant</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SKU size</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Thickness mm</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Coil to use</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>MT to make</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Start from</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>SHS 20x20</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C6" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Mother coil — slit first  (1.6 mm, slit to 76 mm)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>18.12</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SHS 20x20</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C7" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (2 × 76 mm)</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E7" s="9" t="n">
         <v>3.87</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>SHS 25x25</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C8" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (2.8 × 95 mm)</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>3.35</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>SHS 25x25</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C9" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (2.5 × 95 mm)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E9" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>SHS 25x25</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C10" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (2.8 × 96 mm)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>3.58</v>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>SHS 50x50</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (3.2 × 193 mm)</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E11" s="9" t="n">
         <v>1.15</v>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>SHS 72x72</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Mother coil — slit first  (3 mm, slit to 281 mm)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Mother coil — slit first  (3.2 mm, slit to 281 mm)</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>SHS 100x100</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C13" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (1.6 × 398 mm)</t>
         </is>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E13" s="9" t="n">
         <v>14.02</v>
       </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>SHS 100x100</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C14" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (2.5 × 395 mm)</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>11.64</v>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>SHS 100x100</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Mother coil — slit first  (2.5 mm, slit to 397 mm)</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>14.39</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -892,15 +866,15 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Mother coil — slit first  (3 mm, slit to 395 mm)</t>
+          <t>Mother coil — slit first  (2.5 mm, slit to 397 mm)</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8.57</v>
+        <v>14.39</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -909,7 +883,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -933,7 +907,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>3.43</v>
+        <v>4.4</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
@@ -942,302 +916,302 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>SHS 100x100</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 392 mm)</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="9" t="n">
         <v>13.73</v>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Hyderabad</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>RHS 80x40</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Baby coil — ready in yard  (2.8 × 234 mm)</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Baby coil — ready in yard  (3 × 235 mm)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>27 Oct</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Lepakshi</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>RHS 80x40</t>
+          <t>SHS 20x20</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Mother coil — slit first  (2 mm, slit to 76 mm)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Lepakshi</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>SHS 25x25</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Baby coil — ready in yard  (2.5 × 95 mm)</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>27 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Lepakshi</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>SHS 50x50</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Mother coil — slit first  (3.2 mm, slit to 235 mm)</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Baby coil — ready in yard  (3 × 195 mm)</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>27 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>Lepakshi</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SHS 20x20</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Mother coil — slit first  (2 mm, slit to 76 mm)</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>SHS 100x100</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Baby coil — ready in yard  (2.5 × 397 mm)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Lepakshi</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>SHS 25x25</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Baby coil — ready in yard  (2.5 × 95 mm)</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>SHS 100x100</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Mother coil — slit first  (3 mm, slit to 395 mm)</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Lepakshi</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>SHS 100x100</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Baby coil — ready in yard  (4 × 391 mm)</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Lepakshi</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>SHS 50x50</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Baby coil — ready in yard  (3 × 195 mm)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>27 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Lepakshi</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>SHS 100x100</t>
         </is>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Baby coil — ready in yard  (2.5 × 397 mm)</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Lepakshi</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>SHS 100x100</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
+      <c r="C25" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Baby coil — ready in yard  (4 × 391 mm)</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>6.96</v>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>27 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>Lepakshi</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>SHS 100x100</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 390 mm)</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="9" t="n">
         <v>1.31</v>
       </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
@@ -1272,40 +1246,40 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>NPMD</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>SHS 25x25</t>
         </is>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C27" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="D27" s="10" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (1.6 × 99 mm)</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="9" t="n">
         <v>1.66</v>
       </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1312,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1345,7 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1378,7 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1411,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1470,73 +1444,73 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>NPMD</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>SHS 40x40</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C33" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (3 × 156 mm)</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="9" t="n">
         <v>16.79</v>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>NPMD</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>SHS 40x40</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (3 × 155 mm)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="12" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1543,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1602,40 +1576,40 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>NPMD</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>SHS 72x72</t>
         </is>
       </c>
-      <c r="C37" s="11" t="n">
+      <c r="C37" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (1.6 × 288 mm)</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="E37" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
@@ -1668,137 +1642,137 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>SHS 25x25</t>
         </is>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C39" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (3 × 97 mm)</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>29 Oct</t>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>30 Oct</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>SHS 60x60</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
+      <c r="C40" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 233 mm)</t>
         </is>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>SHS 60x60</t>
         </is>
       </c>
-      <c r="C41" s="11" t="n">
+      <c r="C41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (5 × 233 mm)</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>SHS 72x72</t>
         </is>
       </c>
-      <c r="C42" s="8" t="n">
+      <c r="C42" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 286 mm)</t>
         </is>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>27 Oct</t>
         </is>
@@ -1904,99 +1878,99 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>SHS 80x80</t>
         </is>
       </c>
-      <c r="C46" s="8" t="n">
+      <c r="C46" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 315 mm)</t>
         </is>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="12" t="n">
         <v>10.96</v>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>03 Nov</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>RHS 122x61</t>
         </is>
       </c>
-      <c r="C47" s="11" t="n">
+      <c r="C47" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="D47" s="10" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 360 mm)</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="E47" s="9" t="n">
         <v>11.58</v>
       </c>
-      <c r="F47" s="10" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>03 Nov</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>Tapi</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>RHS 122x61</t>
         </is>
       </c>
-      <c r="C48" s="8" t="n">
+      <c r="C48" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="10" t="inlineStr">
         <is>
           <t>Baby coil — ready in yard  (4 × 359 mm)</t>
         </is>
       </c>
-      <c r="E48" s="9" t="n">
+      <c r="E48" s="12" t="n">
         <v>6.53</v>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G48" s="10" t="inlineStr">
         <is>
           <t>03 Nov</t>
         </is>
@@ -2015,7 +1989,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Shaded lines need the mother coil slit first — 2 days plus a day of buffer, so 29 Oct rather than 27 Oct. "Start from" is the date for the whole size+thickness: where any part of it waits on slitting, the lot is dated 29 Oct even on its baby-coil lines, so the size is made in one run.</t>
+          <t>Shaded lines need the mother coil slit first — 2 days plus a day of buffer from the snapshot, so 30 Oct rather than 27 Oct. "Start from" is the date for the whole size+thickness: where any part of it waits on slitting, the whole lot carries that date even on its baby-coil lines, so the size is made in one run.</t>
         </is>
       </c>
     </row>
@@ -2029,14 +2003,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>By plant: NPMD 256.1 MT · Hyderabad 119.4 MT · Tapi 74.0 MT · Lepakshi 59.8 MT</t>
+          <t>By plant: NPMD 256.1 MT · Hyderabad 111.7 MT · Tapi 74.0 MT · Lepakshi 67.4 MT</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>44 lines, 24 size-thickness combinations, 509.2 MT. The other 1629 MT of the 2,138 MT owed cannot be made this cycle — no coil of that spec, under a campaign or gauge floor, or missing a SKU/slitting spec.</t>
+          <t>43 lines, 24 size-thickness combinations, 509.2 MT. The other 1629 MT of the 2,138 MT owed cannot be made this cycle — no coil of that spec, under a campaign or gauge floor, or missing a SKU/slitting spec.</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2024,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Same 509.21 MT, nothing added. Columns are the tube thickness.</t>
+          <t>Adds up the lines above exactly as printed — every row ties across to its own TOTAL. Columns are the tube thickness.</t>
         </is>
       </c>
     </row>
@@ -2124,10 +2098,10 @@
         <v>3.87</v>
       </c>
       <c r="D59" s="11" t="n">
-        <v>34.47</v>
+        <v>34.46</v>
       </c>
       <c r="E59" s="11" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="F59" s="11" t="n">
         <v>23.15</v>
@@ -2137,10 +2111,10 @@
       </c>
       <c r="H59" s="11" t="n"/>
       <c r="I59" s="18" t="n">
-        <v>119.35</v>
+        <v>111.75</v>
       </c>
       <c r="J59" s="11" t="n">
-        <v>119.35</v>
+        <v>111.75</v>
       </c>
       <c r="K59" s="11" t="n"/>
     </row>
@@ -2155,9 +2129,11 @@
         <v>26.13</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="E60" s="11" t="n"/>
+        <v>18.54</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>7.6</v>
+      </c>
       <c r="F60" s="11" t="n">
         <v>6.85</v>
       </c>
@@ -2166,10 +2142,10 @@
       </c>
       <c r="H60" s="11" t="n"/>
       <c r="I60" s="18" t="n">
-        <v>59.79</v>
+        <v>67.39</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>59.79</v>
+        <v>67.39</v>
       </c>
       <c r="K60" s="11" t="n"/>
     </row>
@@ -2276,7 +2252,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G48"/>
+  <autoFilter ref="A5:G48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>